--- a/artfynd/A 38281-2024 artfynd.xlsx
+++ b/artfynd/A 38281-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119559201</v>
+        <v>119559203</v>
       </c>
       <c r="B2" t="n">
-        <v>79607</v>
+        <v>79608</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119559203</v>
+        <v>119559201</v>
       </c>
       <c r="B3" t="n">
-        <v>79608</v>
+        <v>79607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 38281-2024 artfynd.xlsx
+++ b/artfynd/A 38281-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119559203</v>
+        <v>119559201</v>
       </c>
       <c r="B2" t="n">
-        <v>79608</v>
+        <v>79607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119559201</v>
+        <v>119559203</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
+        <v>79608</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 38281-2024 artfynd.xlsx
+++ b/artfynd/A 38281-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119559201</v>
+        <v>119559203</v>
       </c>
       <c r="B2" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119559203</v>
+        <v>119559201</v>
       </c>
       <c r="B3" t="n">
-        <v>79608</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 38281-2024 artfynd.xlsx
+++ b/artfynd/A 38281-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119559203</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,8 +884,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119559201</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>